--- a/docs/machines_balance.xlsx
+++ b/docs/machines_balance.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Машины и логистика" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ребаланс — находки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Машины и логистика (0.3.64)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="0.3.64 было→стало" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>24 000</t>
+          <t>16 004</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>Паразит −1 GTH/t. Одна топка (9 GTH/t) кормит котёл (22 GTH/t) на ~41% времени</t>
+          <t>Паразит −1 GTH/t. Одна топка кормит котёл (58 GTH/t приёма) на ~15% времени — GTH дорог после ребаланса</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>24 000</t>
+          <t>16 004</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>вода 80</t>
+          <t>вода 82</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>вода 12 000; пар 12 000</t>
+          <t>вода 8 000; пар 8 000</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>пар 80</t>
+          <t>пар 82</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>122</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>2 (произв.)</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>пар 12 000; конденсат 2 000</t>
+          <t>пар 6 000; конденсат 2 000</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>Без конденсаторов 85% пара в никуда. 1 стирлинг едва тянет химзавод (1.9)</t>
+          <t>ОТДАЧА 32 GTU/т — потолок выдачи; без конденсаторов 85% пара в никуда</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>4 800</t>
+          <t>3 648</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
-          <t>Полный заряд ~9.4 ч АФК</t>
+          <t>Провод T1 38 &gt; 32 — аккум больше не душит провод</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>1 200</t>
+          <t>362</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>362</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>16 080</t>
+          <t>5 202</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1387,17 +1387,17 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>Дробление 100→80 т (по буферу)</t>
+          <t>Дробление 410→280 т (по буферу)</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>4.0→5.5 GTU/т</t>
+          <t>0.976→1.571 GTU/т</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>400–440 GTU</t>
+          <t>400–440 GTU (как было — время дольше)</t>
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
-          <t>Буфер-гигафон 16 080; в 4.4× дороже T2-измельчителя</t>
+          <t>0.3.64: время ×4…×3.5, расход прежний</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>24 060</t>
+          <t>2 202</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>вода 1 000 / пар 1 000</t>
+          <t>вода 256 / пар 256 (=кипяток)</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>кипяток 12 000 (+скрытая вода 12 000)</t>
+          <t>кипяток 8 000 (+скрытая вода 6 000)</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1464,17 +1464,17 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>Промывка 240 т; нагрев воды 16 mB/т</t>
+          <t>Промывка 310 т; нагрев воды 16 mB/т</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>1.525 GTU/т + 4–5 mB кипятка; нагрев 1.6 GTU/т</t>
+          <t>1.18 GTU/т + кипяток; нагрев 1.6 GTU/т</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>366 GTU + 1 000 mB кипятка</t>
+          <t>366 GTU + 1 000 mB кипятка (как было)</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
-          <t>Паразиты: −0.01 GTU/т, −1 mB кипяток/т</t>
+          <t>0.3.64: время ×1.29, расход прежний; пар 1:1 в кипяток</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>128</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>24 301</t>
+          <t>18 302</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>сусло 492</t>
+          <t>сусло 392</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
-          <t>Алкоголь сусла ≤30%</t>
+          <t>Алкоголь сусла ≤30%; шкалы кратны 128 ✓</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>128</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>392</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>128</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>сырец 8 040; вода 2 006; выход 6 096; кипяток 512</t>
+          <t>сырец 8 064; вода 2 048; выход 8 064; кипяток 512</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>392</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>Все шкалы кратны 128 ✓</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>8 490</t>
+          <t>10 368</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>128</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>дистиллят 10 012; ректификат 7 200</t>
+          <t>дистиллят 9 984; ректификат 7 168</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>392</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>Приём GTU 66 не менялся (не указан)</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>Шкалы кратны 128 ✓</t>
         </is>
       </c>
     </row>
@@ -1918,17 +1918,17 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>кипяток 492</t>
+          <t>кипяток 392</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>кипяток 8 000; вода 8 000</t>
+          <t>кипяток 8 064; вода 8 064</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>вода 492</t>
+          <t>вода 392</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>0.3.64: шкалы 8 000→8 064 (кратность 128)</t>
         </is>
       </c>
     </row>
@@ -1965,29 +1965,29 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
+          <t>8 808</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>2 000</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>2 000</t>
-        </is>
-      </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
           <t>−</t>
@@ -2010,17 +2010,17 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>Строительство/заливка по схеме</t>
+          <t>Рецепты: 75/165/270/30/150/90 т; выпарка 120 т (все ×1.5)</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>по операции</t>
+          <t>по рецепту (GTH/t и GTU/t прежние)</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>×1.5 к прежней</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>Канистра опустошается по 128 mB/т (не мгновенно); смена баков 32 GTU</t>
         </is>
       </c>
     </row>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>2 600</t>
+          <t>10 840</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2087,17 +2087,17 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>Реакция: 160 т</t>
+          <t>Реакция: 240 т (было 160)</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>1.9 GTU/т</t>
+          <t>1.9 GTU/т (прежний)</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>304 GTU/реакцию</t>
+          <t>456 GTU/реакцию (было 304)</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
-          <t>Катализаторы 3 слота, сетка 3×3, шлак 4–6</t>
+          <t>×1.5 время и ×1.5 расход; катализаторы 3, сетка 3×3, шлак 4–6</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
-          <t>Буферы и лимиты = база × M(N), M=N·(1−(N/100)^1.778); N≥100 не строится; макс 8 маршрутов выдачи/т</t>
+          <t>0.3.64: НЕ ТРОНУТА. M(N)=N·(1−(N/100)^1.778), пик N≈56 (61.4 GTU/t)</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>Цикл: 15 mB воды + 11 GTH → 12 mB пара × M</t>
+          <t>Цикл: 16 mB воды + 12 GTH → 12 mB пара × M</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>M = 1 + E_avg·(1+0.1(n−1)), потолок 3.625 (26 платины)</t>
+          <t>M = 1 + 0.93·E_avg·(1+0.1(n−1)); плато 25я+2о ≈ 1 502 mB/t; 1я+26о = 117 mB/t, 92.2 GTU/1000 GTH</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
-          <t>Потери: 2 GTH/т + 1 mB пара/т. Ядра — throughput, теплообменники — эффективность</t>
+          <t>0.3.64: варка 15→16 mB и 11→12 GTH, E ×0.93 — обменники бьются, плато сохранено</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>Транспортировка GTU</t>
+          <t>GTU</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
-          <t>Нет буфера: «вынос слива за пределы блока»</t>
+          <t>0.3.64: НЕ ТРОНУТ (38)</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>388 (сеть)</t>
+          <t>256 (сеть)</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>Транспортировка GTH</t>
+          <t>GTH</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>было 388</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>1 000</t>
+          <t>392</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>1 000</t>
+          <t>392</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>было 1 000</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>1 000</t>
+          <t>392</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>1 000</t>
+          <t>392</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>было 1 000</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>800 (сумма)</t>
+          <t>316 (сумма)</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>800 (сумма)</t>
+          <t>316 (сумма)</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>800 &lt; 1000 обычных: −20% за универсальность</t>
+          <t>−</t>
         </is>
       </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
-          <t>В T2: 1 500</t>
+          <t>было 800</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>Предметы: 5 шт/т на трубу</t>
+          <t>Предметы: 5 шт/т</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
-          <t>Один вид едет не быстрее 1 шт/т</t>
+          <t>не тронута; вид ≤1 шт/т</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>Маршрутизация предметов</t>
+          <t>Маршрутизация</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
@@ -2814,14 +2814,14 @@
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>Фильтр: 3 слота фильтра (макс 5), буфер 5</t>
+          <t>не тронуты</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Универсальный узел</t>
+          <t>Универсальный узел (T1)</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>Соединяет ЛЮБЫЕ сети</t>
+          <t>Любые сети</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -2886,12 +2886,12 @@
       </c>
       <c r="N35" s="5" t="inlineStr">
         <is>
-          <t>−0.1 ко всем пропускностям через узел</t>
+          <t>−0.1 ко всем пропускностям</t>
         </is>
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>БЕЗ потерь на блок — «легальный эксплойт»</t>
+          <t>×0.9 ОТ НОВЫХ значений; без потерь на блок</t>
         </is>
       </c>
     </row>
@@ -2910,12 +2910,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>64 (!)</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>8 400</t>
+          <t>5 202</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>220 GTU/предмет (+10% к T1)</t>
+          <t>220 GTU/предмет</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t>ПРИЁМ ОСТАЛСЯ 64 GTU/t как у T1 — узкое место заправки</t>
+          <t>СВОЙ приём 48 (раньше делила 64 с T1)</t>
         </is>
       </c>
     </row>
@@ -2987,12 +2987,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>644</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -3032,17 +3032,17 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>Измельчение: 35 т</t>
+          <t>Измельчение: 160 т (было 35)</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>2.6 GTU/т</t>
+          <t>0.9 GTU/т</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>91 GTU/операцию</t>
+          <t>144 GTU/операцию</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>В 4.4× дешевле дробилки T1</t>
+          <t>×4.6 время, +58% расход</t>
         </is>
       </c>
     </row>
@@ -3064,12 +3064,12 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>2 482</t>
+          <t>1 876</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>Штамповка: мгновенный ход, КД 60 т</t>
+          <t>Штамповка: мгновенный ход, КД 140 т (было 60)</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="N39" s="5" t="inlineStr">
         <is>
-          <t>≈2.1 GTU/т в среднем</t>
+          <t>≈0.9 GTU/т в среднем</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>1 200</t>
+          <t>644</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>вода 24 000</t>
+          <t>вода 21 000</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>вода 612</t>
+          <t>вода 396</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>Слив в 4× быстрее T1</t>
+          <t>Слив 396 (было 612)</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -3248,12 +3248,12 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>вода 1 000</t>
+          <t>вода 368</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>вода 12 000</t>
+          <t>вода 9 000</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -3263,17 +3263,17 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>1 камень: 60 т</t>
+          <t>1 камень: 80 т (было 60)</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>1.4 GTU/т + 1 000 mB</t>
+          <t>1.05 GTU/т + 1 000 mB</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>84 GTU + 1 000 mB</t>
+          <t>84 GTU + 1 000 mB (как было)</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>3% уголь. В 2.9× быстрее и в 2.1× дешевле T1</t>
+          <t>Время ×1.33, расход прежний</t>
         </is>
       </c>
     </row>
@@ -3300,12 +3300,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>48 900</t>
+          <t>32 608</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>Стор −33%, отдача −15%</t>
         </is>
       </c>
     </row>
@@ -3372,12 +3372,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>1 640</t>
+          <t>2 202</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
-          <t>Сетка 5×5</t>
+          <t>Операция не тронута</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>96 (сеть)</t>
+          <t>89 (сеть)</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>89</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
-          <t>×2.53 к T1 по капе</t>
+          <t>было 96</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>696 (сеть)</t>
+          <t>562 (сеть)</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>×1.79 к T1</t>
+          <t>было 696</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>1 900</t>
+          <t>852</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>1 900</t>
+          <t>852</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
-          <t>×1.9 к T1</t>
+          <t>было 1 900</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>2 шт/т на вид (против 1 у T1)</t>
+          <t>не тронута; 2 шт/т на вид</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>1 500 (сумма)</t>
+          <t>682 (сумма)</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>1 500 (сумма)</t>
+          <t>682 (сумма)</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
@@ -3829,19 +3829,19 @@
       </c>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t>T1: 800</t>
+          <t>было 1 500</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Универсальный узел II</t>
+          <t>Универсальный узел (T2)</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>×0.9</t>
+          <t>×0.91</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>×0.9</t>
+          <t>×0.91</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>×0.9</t>
+          <t>×0.91</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>×0.9</t>
+          <t>×0.91</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>×0.9</t>
+          <t>×0.91</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>×0.9</t>
+          <t>×0.91</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
-          <t>Без потерь</t>
+          <t>0.3.64: ×0.9→×0.91 от новых значений</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -3970,17 +3970,17 @@
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>Горение: 262 GTH/т пока горит топливо</t>
+          <t>Горение: 116 GTH/т (было 262) пока горит топливо</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>262 GTH/т</t>
+          <t>116 GTH/т</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>U слиток: 900 с = 4 716 GTH; брусок 8 100 с = 42 444 GTH</t>
+          <t>U слиток: 900 с = 2 088 GTH; брусок 8 100 с = 18 792 GTH</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="O52" s="5" t="inlineStr">
         <is>
-          <t>&gt;50 000 — поджог, &gt;64 000 — кориум 3×3 (льгота 20 с). Уран: слиток 900 с / кусок 100 с / брусок 8 100 с; торий 300/35/2 700 с; уранит 500 с; торианит 175 с</t>
+          <t>&gt;50 000 — поджог, &gt;64 000 — кориум 3×3. Торий 300/35/2 700 с; уранит 500 с; торианит 175 с (времена не тронуты)</t>
         </is>
       </c>
     </row>
@@ -4062,12 +4062,12 @@
       </c>
       <c r="N53" s="5" t="inlineStr">
         <is>
-          <t>−66 GTH/т + 32 GTH/т за блок сверхплотного льда</t>
+          <t>−66 GTH/т + 32 GTH/т за сверхплотный лёд</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
         <is>
-          <t>&gt;50 000 — поджог, &gt;94 000 — лава 3×3</t>
+          <t>Не тронут (приём 488 &gt; отдача топки 282 — течёт с запасом)</t>
         </is>
       </c>
     </row>
@@ -4086,12 +4086,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>29 086</t>
+          <t>6 204</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="O55" s="5" t="inlineStr">
         <is>
-          <t>Простой: 0.003 GTU/т. Автоматизация: чип-супы в слот 0, готовые чипы и шлак 4–6</t>
+          <t>0.3.64: приём 96 (было 161), стор 6 204 (было 29 086)</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>2 040</t>
+          <t>2 202</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="N56" s="5" t="inlineStr">
         <is>
-          <t>+0.01%/т качества комнаты</t>
+          <t>+0.01%/т качества</t>
         </is>
       </c>
       <c r="O56" s="5" t="inlineStr">
         <is>
-          <t>Уголь 60 с / катализатор 180 с на цикл</t>
+          <t>0.3.64: приём 52 (было 32 — бафф), стор 2 202</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="O57" s="5" t="inlineStr">
         <is>
-          <t>Без GTU; в помещении −3.0 качества за единицу грязи игрока</t>
+          <t>Не тронут</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="O59" s="5" t="inlineStr">
         <is>
-          <t>Нет буфера</t>
+          <t>Не тронут</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>Предлагает поток напрямую в маршруты</t>
+          <t>Предлагает поток напрямую</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="O60" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>Не тронут</t>
         </is>
       </c>
     </row>
@@ -4501,274 +4501,1023 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>№</t>
+          <t>Объект</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Тема</t>
+          <t>Параметр</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Числа</t>
+          <t>Было</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Комментарий</t>
+          <t>Стало</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="n">
-        <v>1</v>
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Пароген 5×5×5</t>
+        </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>Дробилка T1 vs Измельчитель T2</t>
+          <t>Вода на цикл</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>400–440 GTU против 91 GTU за операцию (в 4.4×)</t>
+          <t>15 mB</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>T1-дробилка дороже T2-измельчителя и по энергии, и по времени (80–100 т против 35 т). Если задумано как «дорогой вход в эру» — ок, но выглядит несогласованным</t>
+          <t>16 mB</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="n">
-        <v>2</v>
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Пароген 5×5×5</t>
+        </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Электропечь II жрёт больше T1</t>
+          <t>GTH на цикл</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>220 GTU/предмет против 200 (+10%), время 90 т против 125</t>
+          <t>11 GTH</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>Т2 быстрее, но энергетически хуже. Заодно приём T2 остался 64 GTU/t — заправка буфера 8 400 GTU через 64/t ≈ 131 т только на залив</t>
+          <t>12 GTH</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="n">
-        <v>3</v>
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Пароген 5×5×5</t>
+        </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Стирлинг vs химзавод</t>
+          <t>E теплообменников</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>2 GTU/t против 1.9 GTU/t</t>
+          <t>(C+H)/200</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Один стирлинг тянет завод впритык, без запаса. Два — уже 50% перерасход пара</t>
+          <t>(C+H)/200 × 0.93 (−7%)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="n">
-        <v>4</v>
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Топка</t>
+        </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Помпа жрёт всегда</t>
+          <t>стор GTH</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>T1 2.8 GTU/t, T2 3.0 GTU/t постоянно</t>
+          <t>24 000</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Работает даже без воды рядом — возможно задумано, но «дежурное» потребление бьёт по раннему этапу</t>
+          <t>16 004</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n">
-        <v>5</v>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Котёл</t>
+        </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Центрифуга дороже дробления</t>
+          <t>стор GTH / приём GTH/t</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>366 GTU + 1 000 mB кипятка за 240 т</t>
+          <t>24 000 / 64</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Промывка сырой руды дороже самого дробления, плюс требует кипяток</t>
+          <t>16 004 / 58</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
-        <v>6</v>
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Котёл</t>
+        </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Универсальная жидкостная труба</t>
+          <t>приём воды / стор воды / стор пара / отдача пара</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>T1: 800 против 1000 обычных; T2: 1 500 против 1 900</t>
+          <t>80 / 12 000 / 12 000 / 80</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Универсальность штрафом ~−20% в обоих тирах</t>
+          <t>82 / 8 000 / 8 000 / 82</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
-        <v>7</v>
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Стирлинг</t>
+        </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>Провод T2 vs T1</t>
+          <t>стор GTU / отдача GTU/t / стор пара</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>96 против 38; потеря 0.08→0.09/блок</t>
+          <t>120 / 40 / 12 000</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Капа ×2.5, но потеря на блок выросла — длинные T2-линии теряют больше</t>
+          <t>122 / 32 / 6 000</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
-        <v>8</v>
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Электропечь</t>
+        </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Пресс в среднем</t>
+          <t>приём / стор GTU</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>126 GTU/ход при КД 60 т ≈ 2.1 GTU/t</t>
+          <t>64 / 4 800</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Дешёвый в обслуживании; сравним с химзаводом</t>
+          <t>24 / 3 648</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n">
-        <v>9</v>
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Аккумулятор</t>
+        </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>Солнечная панель ночью</t>
+          <t>приём / отдача GTU/t</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>15 → 0.3 GTU/t (×0.02)</t>
+          <t>64 / 64</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Ночью панель почти мертва; с −1%/день старения к 30-му дню ×0.7</t>
+          <t>32 / 32</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="n">
-        <v>10</v>
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Помпа</t>
+        </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Топка кормит котёл на 41%</t>
+          <t>приём / стор GTU</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>9 GTH/t против аппетита 22 GTH/t</t>
+          <t>64 / 1 200</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Одна топка не тянет даже один котёл непрерывно — цикл работает рывками</t>
+          <t>24 / 362</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="n">
-        <v>11</v>
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Генератор булыжника</t>
+        </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>Булыжник T2 сильно дешевле</t>
+          <t>приём / стор GTU</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>84 GTU/камень против 176 у T1; 60 т против 220 т (рука)</t>
+          <t>64 / 140</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>T2 в 2.1× дешевле по энергии на камень</t>
+          <t>24 / 362</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="n">
-        <v>12</v>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Теплотруба T1</t>
+        </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>Литограф: фотолитография</t>
+          <t>проводимость GTH/t</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>3.8×320 + 28×36 ≈ 2 196 GTU за шаг</t>
+          <t>388</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Спайки дают ~55% бюджета шага; ок если цель — пиковая нагрузка на сеть</t>
+          <t>256</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Жидкостные трубы T1</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>проводимость mB/t</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>1 000</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Универсальная жидкостная T1</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>сумма mB/t</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Универсальный узел T1</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>фактор</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>×0.9 (от старых)</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>×0.9 (от новых)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Дробилка</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>приём / стор GTU</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>214 / 16 080</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>48 / 5 202</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Дробилка</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>длительность / расход</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>100→80 т / 4.0→5.5 GTU/t (400–440)</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>410→280 т / 0.976→1.571 GTU/t (400–440 — те же)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Центрифуга</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>приём / стор GTU</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>192 / 24 060</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>52 / 2 202</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Центрифуга</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>приём вода/пар/кипяток</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>1 000 / 1 000</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>256 / 256</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Центрифуга</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>стор кипятка / скрытая вода / промывка</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>12 000 / 12 000 / 240 т</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>8 000 / 6 000 / 310 т (366 GTU — те же)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Электропечь II</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>приём / стор GTU</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>64 (общий с T1) / 8 400</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>48 (свой) / 5 202</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Измельчитель</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>приём / стор / операция</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>96 / 96 / 35 т × 2.6 = 91 GTU</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>48 / 644 / 160 т × 0.9 = 144 GTU</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Пресс</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>приём / стор / КД</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>128 / 2 482 / 60 т</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>48 / 1 876 / 140 т (126 GTU/ход — те же)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Помпа II</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>приём / стор GTU / стор воды / отдача</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>96 / 1 200 / 24 000 / 612</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>48 / 644 / 21 000 / 396</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Булыжник II</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>приём / вода приём / стор воды / операция</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>64 / 1 000 / 12 000 / 60 т × 1.4 = 84 GTU</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>48 / 368 / 9 000 / 80 т × 1.05 = 84 GTU (те же)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Аккумулятор II</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>стор / отдача</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>48 900 / 144</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>32 608 / 122 (приём 144 — тот же)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Завод сплавов</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>приём / стор GTU</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>220 / 1 640</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>52 / 2 202</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>Провод T2</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>проводимость GTU/t</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>Теплотруба T2</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>проводимость GTH/t</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>Жидкостные трубы T2</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>проводимость mB/t</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>1 900</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>Универсальная жидкостная T2</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>сумма mB/t</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>1 500</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>Универсальный узел T2</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>фактор</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>×0.9</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>×0.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>Ядерная топка</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>горение / отдача GTH/t</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>262 / 488</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>116 / 282 (стор 68 408 — та же)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>Литограф</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>приём / стор GTU</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>161 / 29 086</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>96 / 6 204</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>Фильтр воздуха</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>приём / стор GTU</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>32 / 2 040</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>52 / 2 202</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>Ворт-котёл</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>приём GTH/t / стор GTH / отдача</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>156 / 24 301 / 492</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>128 / 18 302 / 392</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>Чан брожения</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>приём GTH/t / отдача</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>156 / 288</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>128 / 392</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>Дистиллятор</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>приём GTH/t / отдача / шкалы</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>156 / 492 / 8 040·2 006·6 096</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>128 / 392 / 8 064·2 048·8 064 (кратны 128)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>Ректификатор</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>приём GTH/t / стор GTU / отдача / шкалы</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>156 / 8 490 / 492 / 10 012·7 200</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>128 / 10 368 / 392 / 9 984·7 168 (кратны 128)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>Змеевиковый конденсатор</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>отдача/приём / шкалы</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>492 / 8 000·8 000</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>392 / 8 064·8 064 (кратность 128)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>Наполнитель</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>приём / стор GTU</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>66 / 2 000</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>96 / 8 808</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>Наполнитель</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>операции / канистра</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>50·110·180·20·100·60 т; выпарка 80 т; мгновенно</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>75·165·270·30·150·90 т; 120 т (×1.5); по 128 mB/т</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>Химический завод</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>приём / стор / реакция</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>66 / 2 600 / 160 т × 1.9 = 304 GTU</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>96 / 10 840 / 240 т × 1.9 = 456 GTU (×1.5 и время, и расход)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>Узлы (все типы)</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>проводимость</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D45" s="13">
+        <f> трубам соответствующего тира/типа</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>Турбина, солнечная, T1-провод 38, предметы, ядерные времена топлива, T1-булыжник</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>НЕ ТРОНУТЫ (не указаны)</t>
         </is>
       </c>
     </row>

--- a/docs/machines_balance.xlsx
+++ b/docs/machines_balance.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Машины и логистика (0.3.64)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Машины и логистика (0.3.65)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="0.3.64 было→стало" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1488,94 +1488,94 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Доменная печь (мультиблок)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>34 016</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>320 (через узлы)</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Горение топлива ×4 ванили: уголь 20 с вместо 80; 5 топливных слотов</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>34 GTH/t (выработка)</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>выход через 4 узла структуры; TODO: подтвердить отдачу 320</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>0.3.65: структура 3×3×3 шамот+топка+котёл+узлы; слои: низ 9×шамот, середина K+4 узла+4 шамот, верх 8×шамот+котёл; трубы только закладывают топливо</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>ТИР 1 — СИНТЕЗ ЖИДКОСТЕЙ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Ворт-котёл</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>18 302</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>затор 12 288; сусло 12 288</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>сусло 392</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>Кипячение 26 mB/т; испарение 2 mB/т</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>42 GTH/т; 16 GTH/т</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>Алкоголь сусла ≤30%; шкалы кратны 128 ✓</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Чан брожения</t>
+          <t>Ворт-котёл</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>5 040 (+30 000 вольфрам)</t>
+          <t>18 302</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>затор 16 384</t>
+          <t>затор 12 288; сусло 12 288</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>сусло 392</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>Брожение (пассивно)</t>
+          <t>Кипячение 26 mB/т; испарение 2 mB/т</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>68 GTH/т</t>
+          <t>42 GTH/т; 16 GTH/т</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1645,14 +1645,14 @@
       </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
-          <t>Алкоголь ≤13%, rot ≤98%</t>
+          <t>Алкоголь сусла ≤30%; шкалы кратны 128 ✓</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Дистиллятор</t>
+          <t>Чан брожения</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>12 096</t>
+          <t>5 040 (+30 000 вольфрам)</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>сырец 8 064; вода 2 048; выход 8 064; кипяток 512</t>
+          <t>затор 16 384</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1702,12 +1702,12 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>Перегонка: 11 сырца + 20 воды / т</t>
+          <t>Брожение (пассивно)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>64 GTH/т</t>
+          <t>68 GTH/т</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
@@ -1722,24 +1722,24 @@
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>Все шкалы кратны 128 ✓</t>
+          <t>Алкоголь ≤13%, rot ≤98%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Ректификатор</t>
+          <t>Дистиллятор</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>−</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>10 368</t>
+          <t>−</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>6 912</t>
+          <t>12 096</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>дистиллят 9 984; ректификат 7 168</t>
+          <t>сырец 8 064; вода 2 048; выход 8 064; кипяток 512</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1779,12 +1779,12 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>2 дистиллята → 1 ректификат</t>
+          <t>Перегонка: 11 сырца + 20 воды / т</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>6 GTH/т + 9 GTU/т (за тик цикла)</t>
+          <t>64 GTH/т</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
@@ -1799,24 +1799,24 @@
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t>Приём GTU 66 не менялся (не указан)</t>
+          <t>Все шкалы кратны 128 ✓</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Раздаточный кран</t>
+          <t>Ректификатор</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>10 368</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>128</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>6 912</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -1846,22 +1846,22 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>дистиллят 256; сусло 1 024</t>
+          <t>дистиллят 9 984; ректификат 7 168</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>392</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>Розлив вёдра/пузырьки</t>
+          <t>2 дистиллята → 1 ректификат</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>6 GTH/т + 9 GTU/т (за тик цикла)</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
@@ -1876,14 +1876,14 @@
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>Шкалы кратны 128 ✓</t>
+          <t>Приём GTU 66 не менялся (не указан)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Змеевиковый конденсатор</t>
+          <t>Раздаточный кран</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1918,22 +1918,22 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>кипяток 392</t>
+          <t>−</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>кипяток 8 064; вода 8 064</t>
+          <t>дистиллят 256; сусло 1 024</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>вода 392</t>
+          <t>−</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>Кипяток→вода, охлаждение 2 mB/т (база)</t>
+          <t>Розлив вёдра/пузырьки</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
@@ -1953,24 +1953,24 @@
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
-          <t>0.3.64: шкалы 8 000→8 064 (кратность 128)</t>
+          <t>Шкалы кратны 128 ✓</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Наполнитель (Filler)</t>
+          <t>Змеевиковый конденсатор</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>−</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>8 808</t>
+          <t>−</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2 000</t>
+          <t>−</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -1995,32 +1995,32 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>кипяток 392</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>танк 9 000</t>
+          <t>кипяток 8 064; вода 8 064</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>вода 392</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>Рецепты: 75/165/270/30/150/90 т; выпарка 120 т (все ×1.5)</t>
+          <t>Кипяток→вода, охлаждение 2 mB/т (база)</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>по рецепту (GTH/t и GTU/t прежние)</t>
+          <t>−</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>×1.5 к прежней</t>
+          <t>−</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
@@ -2030,356 +2030,356 @@
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
-          <t>Канистра опустошается по 128 mB/т (не мгновенно); смена баков 32 GTU</t>
+          <t>0.3.64: шкалы 8 000→8 064 (кратность 128)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t>Наполнитель (Filler)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>8 808</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>2 000</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>танк 9 000</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Рецепты: 75/165/270/30/150/90 т; выпарка 120 т (все ×1.5)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>по рецепту (GTH/t и GTU/t прежние)</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>×1.5 к прежней</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>Канистра опустошается по 128 mB/т (не мгновенно); смена баков 32 GTU</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t>Химический завод</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>10 840</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>Реакция: 240 т (было 160)</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>1.9 GTU/т (прежний)</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M24" s="5" t="inlineStr">
         <is>
           <t>456 GTU/реакцию (было 304)</t>
         </is>
       </c>
-      <c r="N23" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="O23" s="5" t="inlineStr">
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
         <is>
           <t>×1.5 время и ×1.5 расход; катализаторы 3, сетка 3×3, шлак 4–6</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>МНОГОБЛОКИ (паровая эра)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Паровая турбина (многоблок)</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>64 × рот.</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>пар 100 × рот.</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>пар 1 000 × рот.</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>Пар→GTU: 64 mB/т на ротор</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>64 mB пара/т на ротор</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>56 mB → 1.5 GTU (эталон)</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="inlineStr">
-        <is>
-          <t>26.8 GTU / 1 000 mB пара</t>
-        </is>
-      </c>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>0.3.64: НЕ ТРОНУТА. M(N)=N·(1−(N/100)^1.778), пик N≈56 (61.4 GTU/t)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>Паровая турбина (многоблок)</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>64 × рот.</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>пар 100 × рот.</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>пар 1 000 × рот.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Пар→GTU: 64 mB/т на ротор</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>64 mB пара/т на ротор</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>56 mB → 1.5 GTU (эталон)</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>26.8 GTU / 1 000 mB пара</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>0.3.64: НЕ ТРОНУТА. M(N)=N·(1−(N/100)^1.778), пик N≈56 (61.4 GTU/t)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>Парогенератор 5×5×5</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>4 096 × ядро</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>вода 128 × ядро</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>вода 488 × ядро; пар 1 526 × ядро</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>пар 128 × ядро</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>Цикл: 16 mB воды + 12 GTH → 12 mB пара × M</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>до 34 mB пара/т на ядро (до множителя)</t>
         </is>
       </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t>M = 1 + 0.93·E_avg·(1+0.1(n−1)); плато 25я+2о ≈ 1 502 mB/t; 1я+26о = 117 mB/t, 92.2 GTU/1000 GTH</t>
         </is>
       </c>
-      <c r="O26" s="5" t="inlineStr">
+      <c r="O27" s="5" t="inlineStr">
         <is>
           <t>0.3.64: варка 15→16 mB и 11→12 GTH, E ×0.93 — обменники бьются, плато сохранено</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>ЛОГИСТИКА ТИР 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Провод (T1)</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>38 (сеть)</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>− (пассивен)</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>GTU</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t>потеря 0.08 GTU/блок</t>
-        </is>
-      </c>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>0.3.64: НЕ ТРОНУТ (38)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Теплотруба (T1)</t>
+          <t>Провод (T1)</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>38 (сеть)</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>− (пассивен)</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>38</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>256 (сеть)</t>
+          <t>−</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>−</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>GTH</t>
+          <t>GTU</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -2424,19 +2424,19 @@
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
-          <t>потеря 0.22 GTH/блок</t>
+          <t>потеря 0.08 GTU/блок</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>было 388</t>
+          <t>0.3.64: НЕ ТРОНУТ (38)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Водная труба (T1)</t>
+          <t>Теплотруба (T1)</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>256 (сеть)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>−</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>−</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>Вода</t>
+          <t>GTH</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
@@ -2501,19 +2501,19 @@
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>потеря 0.22 GTH/блок</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>было 1 000</t>
+          <t>было 388</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Паровая труба (T1)</t>
+          <t>Водная труба (T1)</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>Пар</t>
+          <t>Вода</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -2590,7 +2590,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Универсальная жидкостная труба (T1)</t>
+          <t>Паровая труба (T1)</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>316 (сумма)</t>
+          <t>392</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>316 (сумма)</t>
+          <t>392</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>Вода + пар общим бюджетом</t>
+          <t>Пар</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
@@ -2660,14 +2660,14 @@
       </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
-          <t>было 800</t>
+          <t>было 1 000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Предметная труба (T1)</t>
+          <t>Универсальная жидкостная труба (T1)</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>316 (сумма)</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>316 (сумма)</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>Предметы: 5 шт/т</t>
+          <t>Вода + пар общим бюджетом</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2737,14 +2737,14 @@
       </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
-          <t>не тронута; вид ≤1 шт/т</t>
+          <t>было 800</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Предметный узел / фильтр / собиратель (T1)</t>
+          <t>Предметная труба (T1)</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>Маршрутизация</t>
+          <t>Предметы: 5 шт/т</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
@@ -2814,175 +2814,175 @@
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>не тронуты</t>
+          <t>не тронута; вид ≤1 шт/т</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
+          <t>Предметный узел / фильтр / собиратель (T1)</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>Маршрутизация</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>не тронуты</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
           <t>Универсальный узел (T1)</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>×0.9</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>×0.9</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>×0.9</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>×0.9</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>×0.9</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>×0.9</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>Любые сети</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
         <is>
           <t>−0.1 ко всем пропускностям</t>
         </is>
       </c>
-      <c r="O35" s="5" t="inlineStr">
+      <c r="O36" s="5" t="inlineStr">
         <is>
           <t>×0.9 ОТ НОВЫХ значений; без потерь на блок</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>ТИР 2 — ЗАВОДЫ</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Электропечь II</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>5 202</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>Переплавка: 90 т/предмет</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>2.444 GTU/т</t>
-        </is>
-      </c>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>220 GTU/предмет</t>
-        </is>
-      </c>
-      <c r="N37" s="5" t="inlineStr">
-        <is>
-          <t>222% ванильной скорости</t>
-        </is>
-      </c>
-      <c r="O37" s="5" t="inlineStr">
-        <is>
-          <t>СВОЙ приём 48 (раньше делила 64 с T1)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Измельчитель</t>
+          <t>Электропечь II</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>5 202</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -3032,34 +3032,34 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>Измельчение: 160 т (было 35)</t>
+          <t>Переплавка: 90 т/предмет</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>0.9 GTU/т</t>
+          <t>2.444 GTU/т</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>144 GTU/операцию</t>
+          <t>220 GTU/предмет</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>222% ванильной скорости</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>×4.6 время, +58% расход</t>
+          <t>СВОЙ приём 48 (раньше делила 64 с T1)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Пресс</t>
+          <t>Измельчитель</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>1 876</t>
+          <t>644</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -3109,34 +3109,34 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>Штамповка: мгновенный ход, КД 140 т (было 60)</t>
+          <t>Измельчение: 160 т (было 35)</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>− (разово)</t>
+          <t>0.9 GTU/т</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>126 GTU/ход</t>
+          <t>144 GTU/операцию</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr">
         <is>
-          <t>≈0.9 GTU/т в среднем</t>
+          <t>−</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>×4.6 время, +58% расход</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Помпа II</t>
+          <t>Пресс</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>1 876</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -3176,44 +3176,44 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>вода 21 000</t>
+          <t>−</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>вода 396</t>
+          <t>−</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>Всасывание каждые 4 т</t>
+          <t>Штамповка: мгновенный ход, КД 140 т (было 60)</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>3.0 GTU/т</t>
+          <t>− (разово)</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>≈3.0 GTU на 1 000 mB</t>
+          <t>126 GTU/ход</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>≈0.9 GTU/т в среднем</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>Слив 396 (было 612)</t>
+          <t>−</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Генератор булыжника II</t>
+          <t>Помпа II</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -3248,32 +3248,32 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>вода 368</t>
+          <t>−</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>вода 9 000</t>
+          <t>вода 21 000</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>вода 396</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>1 камень: 80 т (было 60)</t>
+          <t>Всасывание каждые 4 т</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>1.05 GTU/т + 1 000 mB</t>
+          <t>3.0 GTU/т</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>84 GTU + 1 000 mB (как было)</t>
+          <t>≈3.0 GTU на 1 000 mB</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr">
@@ -3283,29 +3283,29 @@
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>Время ×1.33, расход прежний</t>
+          <t>Слив 396 (было 612)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Аккумулятор II</t>
+          <t>Генератор булыжника II</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>32 608</t>
+          <t>644</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>−</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>вода 368</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>вода 9 000</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -3340,200 +3340,200 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>Пассивный буфер</t>
+          <t>1 камень: 80 т (было 60)</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>1.05 GTU/т + 1 000 mB</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>84 GTU + 1 000 mB (как было)</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
-          <t>саморазряд 0.01 GTU/т</t>
+          <t>−</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>Стор −33%, отдача −15%</t>
+          <t>Время ×1.33, расход прежний</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
+          <t>Аккумулятор II</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>32 608</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>Пассивный буфер</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>саморазряд 0.01 GTU/т</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>Стор −33%, отдача −15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
           <t>Завод сплавов</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>2 202</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>Плавка: 80 т + 8 т/ингредиент</t>
         </is>
       </c>
-      <c r="L43" s="5" t="inlineStr">
+      <c r="L44" s="5" t="inlineStr">
         <is>
           <t>2.8 GTU/т</t>
         </is>
       </c>
-      <c r="M43" s="5" t="inlineStr">
+      <c r="M44" s="5" t="inlineStr">
         <is>
           <t>224 + 22.4·n GTU</t>
         </is>
       </c>
-      <c r="N43" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
         <is>
           <t>Операция не тронута</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>ЛОГИСТИКА ТИР 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Провод (T2)</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>89 (сеть)</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>GTU</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="N45" s="5" t="inlineStr">
-        <is>
-          <t>потеря 0.09 GTU/блок</t>
-        </is>
-      </c>
-      <c r="O45" s="5" t="inlineStr">
-        <is>
-          <t>было 96</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Теплотруба (T2)</t>
+          <t>Провод (T2)</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>89 (сеть)</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>89</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>562 (сеть)</t>
+          <t>−</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>−</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>GTH</t>
+          <t>GTU</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
@@ -3593,19 +3593,19 @@
       </c>
       <c r="N46" s="5" t="inlineStr">
         <is>
-          <t>потеря 0.18 GTH/блок</t>
+          <t>потеря 0.09 GTU/блок</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>было 696</t>
+          <t>было 96</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Водная / паровая труба (T2)</t>
+          <t>Теплотруба (T2)</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>562 (сеть)</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>−</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>−</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>Вода / пар</t>
+          <t>GTH</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -3670,19 +3670,19 @@
       </c>
       <c r="N47" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>потеря 0.18 GTH/блок</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
-          <t>было 1 900</t>
+          <t>было 696</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Предметная труба (T2)</t>
+          <t>Водная / паровая труба (T2)</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>852</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>852</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>Предметы: 10 шт/т</t>
+          <t>Вода / пар</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
@@ -3752,14 +3752,14 @@
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>не тронута; 2 шт/т на вид</t>
+          <t>было 1 900</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Универсальная жидкостная труба (T2)</t>
+          <t>Предметная труба (T2)</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>682 (сумма)</t>
+          <t>−</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>682 (сумма)</t>
+          <t>−</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>Вода + пар</t>
+          <t>Предметы: 10 шт/т</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -3829,346 +3829,346 @@
       </c>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t>было 1 500</t>
+          <t>не тронута; 2 шт/т на вид</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
+          <t>Универсальная жидкостная труба (T2)</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>682 (сумма)</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>682 (сумма)</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>Вода + пар</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>было 1 500</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
           <t>Универсальный узел (T2)</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>×0.91</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>×0.91</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>×0.91</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>×0.91</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>×0.91</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>×0.91</t>
         </is>
       </c>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="K51" s="5" t="inlineStr">
         <is>
           <t>Любые сети</t>
         </is>
       </c>
-      <c r="L50" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="M50" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="N50" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="O50" s="5" t="inlineStr">
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="inlineStr">
         <is>
           <t>0.3.64: ×0.9→×0.91 от новых значений</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="10" t="inlineStr">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>ТИР 3 — ЯДЕРНОЕ</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>Ядерная топка</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>68 408</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>Горение: 116 GTH/т (было 262) пока горит топливо</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>116 GTH/т</t>
-        </is>
-      </c>
-      <c r="M52" s="5" t="inlineStr">
-        <is>
-          <t>U слиток: 900 с = 2 088 GTH; брусок 8 100 с = 18 792 GTH</t>
-        </is>
-      </c>
-      <c r="N52" s="5" t="inlineStr">
-        <is>
-          <t>−25% времени горения при полном буфере</t>
-        </is>
-      </c>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>&gt;50 000 — поджог, &gt;64 000 — кориум 3×3. Торий 300/35/2 700 с; уранит 500 с; торианит 175 с (времена не тронуты)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
+          <t>Ядерная топка</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>68 408</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>Горение: 116 GTH/т (было 262) пока горит топливо</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>116 GTH/т</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>U слиток: 900 с = 2 088 GTH; брусок 8 100 с = 18 792 GTH</t>
+        </is>
+      </c>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>−25% времени горения при полном буфере</t>
+        </is>
+      </c>
+      <c r="O53" s="5" t="inlineStr">
+        <is>
+          <t>&gt;50 000 — поджог, &gt;64 000 — кориум 3×3. Торий 300/35/2 700 с; уранит 500 с; торианит 175 с (времена не тронуты)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
           <t>Вольфрамовый поглотитель</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>488</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>112 000</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>Пассивное рассеивание</t>
         </is>
       </c>
-      <c r="L53" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="M53" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="N54" s="5" t="inlineStr">
         <is>
           <t>−66 GTH/т + 32 GTH/т за сверхплотный лёд</t>
         </is>
       </c>
-      <c r="O53" s="5" t="inlineStr">
+      <c r="O54" s="5" t="inlineStr">
         <is>
           <t>Не тронут (приём 488 &gt; отдача топки 282 — течёт с запасом)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>ТИР 3 — ЧИСТАЯ КОМНАТА</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>Литограф (Si-фабрика)</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>6 204</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>3 шага: травление 180 т → фотолитография 320 т → вулканизация 90 т</t>
-        </is>
-      </c>
-      <c r="L55" s="5" t="inlineStr">
-        <is>
-          <t>3.8 GTU/т (+ спайк 28 GTU каждые 9 т на фотолитографии)</t>
-        </is>
-      </c>
-      <c r="M55" s="5" t="inlineStr">
-        <is>
-          <t>травление 684; фотолит. ≈2 196; вулк. 342 GTU</t>
-        </is>
-      </c>
-      <c r="N55" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="O55" s="5" t="inlineStr">
-        <is>
-          <t>0.3.64: приём 96 (было 161), стор 6 204 (было 29 086)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Фильтр воздуха</t>
+          <t>Литограф (Si-фабрика)</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>2 202</t>
+          <t>6 204</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -4208,263 +4208,340 @@
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>Очистка комнаты: непрерывно</t>
+          <t>3 шага: травление 180 т → фотолитография 320 т → вулканизация 90 т</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>2.6 GTU/т (работа); утечка 0.019 GTU/т</t>
+          <t>3.8 GTU/т (+ спайк 28 GTU каждые 9 т на фотолитографии)</t>
         </is>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>травление 684; фотолит. ≈2 196; вулк. 342 GTU</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr">
         <is>
-          <t>+0.01%/т качества</t>
+          <t>−</t>
         </is>
       </c>
       <c r="O56" s="5" t="inlineStr">
         <is>
-          <t>0.3.64: приём 52 (было 32 — бафф), стор 2 202</t>
+          <t>0.3.64: приём 96 (было 161), стор 6 204 (было 29 086)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
+          <t>Фильтр воздуха</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>2 202</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>Очистка комнаты: непрерывно</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>2.6 GTU/т (работа); утечка 0.019 GTU/т</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>+0.01%/т качества</t>
+        </is>
+      </c>
+      <c r="O57" s="5" t="inlineStr">
+        <is>
+          <t>0.3.64: приём 52 (было 32 — бафф), стор 2 202</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
           <t>Очиститель воздуха</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>Поток чистоты: импульс 8 с по фронту редстоуна</t>
         </is>
       </c>
-      <c r="L57" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="M57" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="N58" s="5" t="inlineStr">
         <is>
           <t>−11.5 грязи/с в потоке</t>
         </is>
       </c>
-      <c r="O57" s="5" t="inlineStr">
+      <c r="O58" s="5" t="inlineStr">
         <is>
           <t>Не тронут</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>АДМИНСКИЕ / ТЕСТОВЫЕ</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Сингулярный источник энергии</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>− (виртуальный бюджет)</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>100 000 (потолок)</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>Предлагает поток напрямую в маршруты</t>
-        </is>
-      </c>
-      <c r="L59" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="M59" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="N59" s="5" t="inlineStr">
-        <is>
-          <t>Реальный поток режет провод/приёмник</t>
-        </is>
-      </c>
-      <c r="O59" s="5" t="inlineStr">
-        <is>
-          <t>Не тронут</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
+          <t>Сингулярный источник энергии</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>− (виртуальный бюджет)</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>100 000 (потолок)</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>Предлагает поток напрямую в маршруты</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>Реальный поток режет провод/приёмник</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>Не тронут</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
           <t>Сингулярный источник тепла</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>100 000 (потолок)</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="inlineStr">
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
         <is>
           <t>Предлагает поток напрямую</t>
         </is>
       </c>
-      <c r="L60" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="M60" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="N60" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="O60" s="5" t="inlineStr">
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="O61" s="5" t="inlineStr">
         <is>
           <t>Не тронут</t>
         </is>
@@ -4473,17 +4550,17 @@
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="H1:J1"/>
-    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="A55:O55"/>
     <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A25:O25"/>
     <mergeCell ref="M1:M2"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A54:O54"/>
-    <mergeCell ref="A51:O51"/>
+    <mergeCell ref="A59:O59"/>
+    <mergeCell ref="A16:O16"/>
+    <mergeCell ref="A52:O52"/>
+    <mergeCell ref="A28:O28"/>
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="A44:O44"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="A58:O58"/>
+    <mergeCell ref="A45:O45"/>
+    <mergeCell ref="A37:O37"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="O1:O2"/>
@@ -4501,7 +4578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5521,6 +5598,28 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>0.3.65 Доменная печь</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>новая машина</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>мультиблок 3×3×3: 34 GTH/t, жжение ×4 (уголь 20 с), буфер 34 016, 5 слотов топлива (только закладка), GTH через 4 узла (320 GTH/t, ждёт подтверждения); шамотный кирпич: bricks+clay_ball+bone_meal+wheat+calcite → 4, фулл-гейт «Открытие 1»</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/machines_balance.xlsx
+++ b/docs/machines_balance.xlsx
@@ -1521,7 +1521,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>320 (через узлы)</t>
+          <t>144/т на узел (до 576 через 4)</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
-          <t>выход через 4 узла структуры; TODO: подтвердить отдачу 320</t>
+          <t>выход через 4 узла структуры; 144 GTH/т НА УЗЕЛ (автор, 0.3.75); сборка поглощает содержимое топки в 5 слотов и стартует чистой, разбор всё выпадает</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
@@ -4551,20 +4551,20 @@
   <mergeCells count="18">
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A55:O55"/>
-    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A59:O59"/>
     <mergeCell ref="A25:O25"/>
     <mergeCell ref="M1:M2"/>
-    <mergeCell ref="A59:O59"/>
     <mergeCell ref="A16:O16"/>
     <mergeCell ref="A52:O52"/>
     <mergeCell ref="A28:O28"/>
     <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N1:N2"/>
     <mergeCell ref="A45:O45"/>
     <mergeCell ref="A37:O37"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="O1:O2"/>
-    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="A3:O3"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
